--- a/jogos_2025-02-18.xlsx
+++ b/jogos_2025-02-18.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Zrinski Jurjevac</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['73', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.2</v>
       </c>
-      <c r="O2" t="n">
+      <c r="AI2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>3.75</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>['2', '20', '80']</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45706.41666666666</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>EGS Gafsa</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y3" t="n">
         <v>2.3</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="Z3" t="n">
         <v>1.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AA3" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['45+1', '46', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.11</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['73', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45706.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zrinski Jurjevac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EGS Gafsa</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V5" t="n">
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="X5" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['2', '20', '80']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.53</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['45+1', '46', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH5" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45706.41666666666</v>
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Cape Town City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2.9</v>
-      </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="Z10" t="n">
         <v>1.48</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AB10" t="n">
         <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['31', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['17', '82', '90+1']</t>
+          <t>['61', '70']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45706.60416666666</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="P11" t="n">
         <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
         <v>1.57</v>
@@ -1860,7 +1860,7 @@
         <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
         <v>1.5</v>
@@ -1869,44 +1869,44 @@
         <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['3', '32', '63', '83']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45706.60416666666</v>
@@ -1933,33 +1933,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cape Town City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
         <v>3</v>
@@ -1974,13 +1974,13 @@
         <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
         <v>3.75</v>
@@ -1989,53 +1989,53 @@
         <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.9</v>
+        <v>5.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['3', '32', '63', '83']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['61', '70']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45706.60416666666</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Real Kings</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '48']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '82', '90+1']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45706.60416666666</v>
@@ -2191,87 +2191,87 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Real Kings</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2280,20 +2280,20 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45706.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2593,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="M17" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="N17" t="n">
-        <v>3.53</v>
+        <v>2.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
         <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45706.69791666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3.64</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.33</v>
+        <v>4.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45706.69791666666</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="M19" t="n">
         <v>3.47</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>3.57</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
         <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['30', '50']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3109,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,55 +3120,55 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.62</v>
+        <v>3.9</v>
       </c>
       <c r="M21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>1.87</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.98</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -3178,25 +3178,25 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.01</v>
+        <v>1.12</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.91</v>
+        <v>1.44</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.57</v>
+        <v>1.87</v>
       </c>
       <c r="O22" t="n">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC22" t="n">
         <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['30', '50']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.86</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.58</v>
+        <v>1.69</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="N23" t="n">
-        <v>2.58</v>
+        <v>5.2</v>
       </c>
       <c r="O23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.4</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X23" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.44</v>
       </c>
-      <c r="AH23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3496,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.9</v>
+        <v>1.92</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="N24" t="n">
-        <v>1.87</v>
+        <v>3.64</v>
       </c>
       <c r="O24" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.3</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.12</v>
+        <v>1.78</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,109 +3610,109 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P25" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.91</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
         <v>1.8</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['51', '59']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hamilton Academical</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.2</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -3789,59 +3789,59 @@
         <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X26" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD26" t="n">
         <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['28', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['82']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3868,19 +3868,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.99</v>
+        <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>3.59</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>5.9</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.38</v>
+        <v>7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
+          <t>['51', '59']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
       <c r="AG27" t="n">
-        <v>2.05</v>
+        <v>1.08</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>2.9</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.88</v>
+        <v>1.29</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45706.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Hamilton Academical</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,22 +4023,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
         <v>1.4</v>
@@ -4047,31 +4047,31 @@
         <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="X28" t="n">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.98</v>
+        <v>3.42</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AC28" t="n">
         <v>1.8</v>
@@ -4081,25 +4081,25 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
+          <t>['28', '79']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
       <c r="AG28" t="n">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45706.69791666666</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.16</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>8.800000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="N30" t="n">
-        <v>17</v>
+        <v>3.73</v>
       </c>
       <c r="O30" t="n">
-        <v>1.45</v>
+        <v>2.27</v>
       </c>
       <c r="P30" t="n">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>10.2</v>
+        <v>4.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X30" t="n">
         <v>5</v>
       </c>
-      <c r="T30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X30" t="n">
-        <v>10</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['22', '76', '84']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['32', '51', '81']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>5.95</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45706.70833333334</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="M31" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="O31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X31" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2.05</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="AC31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.03</v>
       </c>
-      <c r="W31" t="n">
+      <c r="AH31" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.2</v>
       </c>
-      <c r="X31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['3', '27', '45+3']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45706.70833333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>3.73</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="P32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.24</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V32" t="n">
         <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.48</v>
+        <v>2.07</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['22', '76', '84']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['32', '51', '81']</t>
+          <t>['3', '27', '45+3']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45706.70833333334</v>
@@ -4771,19 +4771,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alianza Lima</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.76</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.26</v>
+        <v>6.5</v>
       </c>
       <c r="O34" t="n">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="P34" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="X34" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.25</v>
+        <v>2.65</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="AH34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI34" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45706.89583333334</v>
@@ -4900,19 +4900,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Alianza Lima</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.5</v>
+        <v>2.76</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="N35" t="n">
-        <v>6.5</v>
+        <v>2.26</v>
       </c>
       <c r="O35" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="P35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X35" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
       <c r="Y35" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="Z35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA35" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['38']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45706.89583333334</v>
